--- a/AAA EAs/BM Trading Robust Sets 2026-08-04/Active Portfolio Full Pipeline 2026-09-05/EA OPTIMIZATION PROGRESS.xlsx
+++ b/AAA EAs/BM Trading Robust Sets 2026-08-04/Active Portfolio Full Pipeline 2026-09-05/EA OPTIMIZATION PROGRESS.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active EAs" sheetId="1" r:id="R46172e79d4a94b4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded" sheetId="2" r:id="R96425f3364d04ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active EAs" sheetId="1" r:id="R554c4a7a703f4c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded" sheetId="2" r:id="R8073ace1f0974f33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1000,22 +1000,22 @@
         <x:v>Active: all BATs and website</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Complete</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
-        <x:v>Original development/locked reconstruction plus Dynamic 50/20 and session audit</x:v>
+        <x:v>67 development configurations; RR 0.5R–5R and adaptive RR; ATR and signal-candle stops; M1/M5/M15/M30; Asia/London/overlap/New York anchors; direction and signal filters; ATR, breakeven, Dynamic and no-management exits; Safe comparison; untouched locked year; exact three years; cost stress; 10,000-path Monte Carlo</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
-        <x:v>Complete modern RR, stop, timeframe, management, exact three-year and Monte Carlo comparison.</x:v>
+        <x:v>None. Continue Standard demo monitoring before real capital.</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>Keep cautiously with Dynamic 50/20 while the full re-audit is pending.</x:v>
+        <x:v>Promote USTEC M5 at 09:30 New York with EMA12, ATR14, 4 ATR stop, fixed 2.5R target, no trailing, both directions and 15:55 close. Standard is recommended; Safe remains optional. Risk stays hard-capped at 1%.</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
-        <x:v>The recreated model is profitable but did not reproduce the advertised results.</x:v>
+        <x:v>Locked year: +38.12%, PF 1.21, 41.41% wins, DD 12.12%, 256 trades. Three years: +100.07%, PF 1.17, 40.29% wins, DD 16.26%, 762 trades, Sharpe 2.89, recovery 3.83. MC P5 +0.60%, profitable paths 95.12%, P95 DD 39.76%.</x:v>
       </x:c>
       <x:c r="K20" s="12" t="n">
-        <x:v>46270</x:v>
+        <x:v>46272</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="72" customHeight="1">
@@ -1349,7 +1349,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaee965a19ed4d5e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R386580189fde4ba9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1561,7 +1561,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb20e0cd5f784bcb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra04b7ff0e6214024"/>
   </x:tableParts>
 </x:worksheet>
 </file>